--- a/results/gcd_progress.xlsx
+++ b/results/gcd_progress.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,7 +558,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2108,60 +2108,28 @@
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>CLNN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2214,12 +2182,12 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2267,12 +2235,12 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2320,7 +2288,7 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2373,7 +2341,7 @@
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2426,93 +2394,93 @@
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="inlineStr">
         <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n"/>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
           <t>TAN</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>[0, 4]</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>clinc</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>ALUP</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>DPN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2565,86 +2533,86 @@
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[0, 4]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
+          <t>[0, 4]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2692,12 +2660,12 @@
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2745,12 +2713,12 @@
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2798,98 +2766,98 @@
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="inlineStr">
         <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n"/>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
           <t>TAN</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[0, 4]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
         <is>
           <t>hwu</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
+      <c r="B51" s="1" t="inlineStr">
         <is>
           <t>ALUP</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n"/>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>DPN</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2937,65 +2905,33 @@
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>CLNN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3043,12 +2979,12 @@
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3096,12 +3032,12 @@
       <c r="A55" s="1" t="n"/>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3149,7 +3085,7 @@
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3202,45 +3138,65 @@
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 3, 4]</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>mcid</t>
-        </is>
-      </c>
+      <c r="A58" s="1" t="n"/>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3288,60 +3244,40 @@
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 4]</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n"/>
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3394,12 +3330,12 @@
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3447,12 +3383,12 @@
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3500,12 +3436,12 @@
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3553,12 +3489,12 @@
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3606,45 +3542,65 @@
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3692,60 +3648,40 @@
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 4]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n"/>
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3798,7 +3734,7 @@
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3851,7 +3787,7 @@
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3904,7 +3840,7 @@
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3957,7 +3893,7 @@
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4010,45 +3946,65 @@
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr">
-        <is>
-          <t>stackoverflow</t>
-        </is>
-      </c>
+      <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4096,60 +4052,40 @@
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n"/>
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4202,60 +4138,28 @@
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>CLNN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4308,12 +4212,12 @@
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>[0, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4361,7 +4265,7 @@
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4414,45 +4318,65 @@
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr">
-        <is>
-          <t>thucnews</t>
-        </is>
-      </c>
+      <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 3, 4]</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4500,12 +4424,12 @@
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4553,101 +4477,85 @@
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 4]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n"/>
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
     </row>
@@ -4655,47 +4563,202 @@
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="inlineStr">
         <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n"/>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n"/>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n"/>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
           <t>TAN</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A4:A11"/>
     <mergeCell ref="A26:A33"/>
-    <mergeCell ref="A58:A65"/>
-    <mergeCell ref="A74:A81"/>
-    <mergeCell ref="A34:A41"/>
+    <mergeCell ref="A43:A50"/>
     <mergeCell ref="A12:A19"/>
-    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="A51:A59"/>
+    <mergeCell ref="A34:A42"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A82:A86"/>
-    <mergeCell ref="A42:A49"/>
-    <mergeCell ref="A66:A73"/>
+    <mergeCell ref="A68:A75"/>
+    <mergeCell ref="A85:A89"/>
+    <mergeCell ref="A60:A67"/>
+    <mergeCell ref="A76:A84"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/gcd_progress.xlsx
+++ b/results/gcd_progress.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 4]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[4]</t>
+          <t>[0, 4]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">

--- a/results/gcd_progress.xlsx
+++ b/results/gcd_progress.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,42 +563,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -616,42 +616,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -669,42 +669,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -717,47 +717,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -775,42 +775,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -828,42 +828,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -881,42 +881,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -929,25 +929,49 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[0, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -967,42 +991,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1044,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1035,12 +1059,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,12 +1074,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1073,42 +1097,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1126,42 +1150,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1179,42 +1203,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1232,42 +1256,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1285,42 +1309,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1333,25 +1357,49 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1371,12 +1419,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1386,12 +1434,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1401,12 +1449,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1419,47 +1467,47 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1472,47 +1520,47 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1525,47 +1573,47 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1626,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>[0, 1, 2, 3]</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3]</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3]</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1631,25 +1679,49 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1664,47 +1736,47 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1717,47 +1789,47 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1770,47 +1842,47 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1823,47 +1895,47 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1876,47 +1948,47 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1929,47 +2001,47 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1982,47 +2054,47 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2107,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2065,42 +2137,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2108,28 +2180,60 @@
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>CLNN</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[0, 4]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2139,42 +2243,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2286,7 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2192,42 +2296,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2235,52 +2339,52 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2392,7 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2298,42 +2402,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2445,7 @@
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2351,42 +2455,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2498,7 @@
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2404,83 +2508,107 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n"/>
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>clinc</t>
+        </is>
+      </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[0, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>clinc</t>
-        </is>
-      </c>
+      <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2490,42 +2618,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2661,7 @@
       <c r="A44" s="1" t="n"/>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2543,42 +2671,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2586,73 +2714,105 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[0, 4]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2820,7 @@
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2670,42 +2830,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2713,52 +2873,52 @@
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2926,7 @@
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2776,83 +2936,107 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n"/>
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[0, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>hwu</t>
-        </is>
-      </c>
+      <c r="A51" s="1" t="n"/>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2862,42 +3046,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2905,28 +3089,60 @@
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>CLNN</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[4]</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2936,42 +3152,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -2979,7 +3195,7 @@
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2989,42 +3205,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3032,52 +3248,52 @@
       <c r="A55" s="1" t="n"/>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3301,7 @@
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3095,42 +3311,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3138,60 +3354,64 @@
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n"/>
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3201,42 +3421,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3244,40 +3464,60 @@
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>[0, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>mcid</t>
-        </is>
-      </c>
+      <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3287,42 +3527,42 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3570,7 @@
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3340,42 +3580,42 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3623,7 @@
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3393,42 +3633,42 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3676,7 @@
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3446,42 +3686,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3729,7 @@
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3499,42 +3739,42 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3782,7 @@
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3552,50 +3792,54 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n"/>
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3605,42 +3849,42 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3648,40 +3892,60 @@
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[0, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3691,42 +3955,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3734,52 +3998,52 @@
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3787,52 +4051,52 @@
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3840,52 +4104,52 @@
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3893,52 +4157,52 @@
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3946,7 +4210,7 @@
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3956,50 +4220,54 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n"/>
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4009,42 +4277,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4052,40 +4320,60 @@
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>stackoverflow</t>
-        </is>
-      </c>
+      <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4095,42 +4383,42 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4138,28 +4426,60 @@
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>CLNN</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4169,42 +4489,42 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4532,7 @@
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4222,42 +4542,42 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4585,7 @@
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4275,42 +4595,42 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4638,7 @@
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4328,95 +4648,99 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n"/>
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>[0, 3, 4]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4748,7 @@
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4434,42 +4758,42 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4477,40 +4801,60 @@
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[0, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="inlineStr">
-        <is>
-          <t>thucnews</t>
-        </is>
-      </c>
+      <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4520,42 +4864,42 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4563,52 +4907,52 @@
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4616,52 +4960,52 @@
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -4669,96 +5013,71 @@
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>TAN</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>[3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>[3]</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="n"/>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>TAN</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A4:A11"/>
     <mergeCell ref="A26:A33"/>
-    <mergeCell ref="A43:A50"/>
+    <mergeCell ref="A58:A65"/>
+    <mergeCell ref="A74:A81"/>
+    <mergeCell ref="A34:A41"/>
     <mergeCell ref="A12:A19"/>
-    <mergeCell ref="A51:A59"/>
-    <mergeCell ref="A34:A42"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="A82:A88"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A68:A75"/>
-    <mergeCell ref="A85:A89"/>
-    <mergeCell ref="A60:A67"/>
-    <mergeCell ref="A76:A84"/>
+    <mergeCell ref="A42:A49"/>
+    <mergeCell ref="A66:A73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/gcd_progress.xlsx
+++ b/results/gcd_progress.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hwu</t>
+          <t>ecdt</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
@@ -2988,47 +2988,47 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
     </row>
@@ -3041,47 +3041,47 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 3]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 3]</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
     </row>
@@ -3089,52 +3089,52 @@
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
     </row>
@@ -3142,52 +3142,52 @@
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
     </row>
@@ -3195,60 +3195,64 @@
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2, 3]</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 1, 2]</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n"/>
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3301,7 +3305,7 @@
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3354,7 +3358,7 @@
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3404,14 +3408,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>mcid</t>
-        </is>
-      </c>
+      <c r="A58" s="1" t="n"/>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3464,7 +3464,7 @@
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3517,7 +3517,7 @@
       <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3570,7 +3570,7 @@
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3623,7 +3623,7 @@
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3673,10 +3673,14 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n"/>
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3729,7 +3733,7 @@
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3782,7 +3786,7 @@
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3832,14 +3836,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3892,7 +3892,7 @@
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3945,7 +3945,7 @@
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3998,7 +3998,7 @@
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4051,7 +4051,7 @@
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4101,10 +4101,14 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n"/>
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4157,7 +4161,7 @@
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4210,7 +4214,7 @@
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4260,14 +4264,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr">
-        <is>
-          <t>stackoverflow</t>
-        </is>
-      </c>
+      <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4320,7 +4320,7 @@
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4373,7 +4373,7 @@
       <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4426,7 +4426,7 @@
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4479,7 +4479,7 @@
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4529,10 +4529,14 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n"/>
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4585,7 +4589,7 @@
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4638,7 +4642,7 @@
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4688,14 +4692,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="inlineStr">
-        <is>
-          <t>thucnews</t>
-        </is>
-      </c>
+      <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4748,7 +4748,7 @@
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4801,12 +4801,12 @@
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4854,12 +4854,12 @@
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4907,7 +4907,7 @@
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4957,10 +4957,14 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n"/>
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5013,71 +5017,390 @@
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="inlineStr">
         <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n"/>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n"/>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n"/>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n"/>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n"/>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n"/>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
           <t>TAN</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A4:A11"/>
+    <mergeCell ref="A79:A86"/>
     <mergeCell ref="A26:A33"/>
-    <mergeCell ref="A58:A65"/>
-    <mergeCell ref="A74:A81"/>
     <mergeCell ref="A34:A41"/>
     <mergeCell ref="A12:A19"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="A82:A88"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A50:A54"/>
+    <mergeCell ref="A87:A94"/>
+    <mergeCell ref="A71:A78"/>
+    <mergeCell ref="A63:A70"/>
+    <mergeCell ref="A55:A62"/>
     <mergeCell ref="A42:A49"/>
-    <mergeCell ref="A66:A73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/gcd_progress.xlsx
+++ b/results/gcd_progress.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1462,7 +1462,7 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1515,7 +1515,7 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1568,7 +1568,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1621,7 +1621,7 @@
       <c r="A24" s="1" t="n"/>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       <c r="A25" s="1" t="n"/>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1724,14 +1724,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>Yahoo</t>
-        </is>
-      </c>
+      <c r="A26" s="1" t="n"/>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1784,7 +1780,7 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1834,10 +1830,14 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n"/>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1943,7 +1943,7 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1996,7 +1996,7 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2049,7 +2049,7 @@
       <c r="A32" s="1" t="n"/>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2102,7 +2102,7 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2110,24 +2110,52 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>banking</t>
-        </is>
-      </c>
+      <c r="A34" s="1" t="n"/>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2180,7 +2208,7 @@
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2230,10 +2258,14 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n"/>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>banking</t>
+        </is>
+      </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2286,7 +2318,7 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2339,7 +2371,7 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2392,7 +2424,7 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2445,7 +2477,7 @@
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2498,7 +2530,7 @@
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2548,14 +2580,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>clinc</t>
-        </is>
-      </c>
+      <c r="A42" s="1" t="n"/>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2608,7 +2636,7 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2658,10 +2686,14 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n"/>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>clinc</t>
+        </is>
+      </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2714,7 +2746,7 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2767,7 +2799,7 @@
       <c r="A46" s="1" t="n"/>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2820,7 +2852,7 @@
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2873,7 +2905,7 @@
       <c r="A48" s="1" t="n"/>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2926,7 +2958,7 @@
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2976,59 +3008,55 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>ecdt</t>
-        </is>
-      </c>
+      <c r="A50" s="1" t="n"/>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3036,105 +3064,109 @@
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[0, 1, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>[0, 1, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n"/>
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>ecdt</t>
+        </is>
+      </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3142,52 +3174,52 @@
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -3195,64 +3227,60 @@
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>hwu</t>
-        </is>
-      </c>
+      <c r="A55" s="1" t="n"/>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3305,7 +3333,7 @@
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3358,7 +3386,7 @@
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3411,7 +3439,7 @@
       <c r="A58" s="1" t="n"/>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3464,7 +3492,7 @@
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3514,10 +3542,14 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n"/>
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3570,7 +3602,7 @@
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3623,7 +3655,7 @@
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3673,14 +3705,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>mcid</t>
-        </is>
-      </c>
+      <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3733,7 +3761,7 @@
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3786,7 +3814,7 @@
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3839,7 +3867,7 @@
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3892,7 +3920,7 @@
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3942,10 +3970,14 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n"/>
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3998,7 +4030,7 @@
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4051,7 +4083,7 @@
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4101,14 +4133,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4161,7 +4189,7 @@
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4214,7 +4242,7 @@
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4267,7 +4295,7 @@
       <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4320,7 +4348,7 @@
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4370,10 +4398,14 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n"/>
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4426,7 +4458,7 @@
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4479,7 +4511,7 @@
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4529,14 +4561,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="inlineStr">
-        <is>
-          <t>stackoverflow</t>
-        </is>
-      </c>
+      <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4589,7 +4617,7 @@
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4642,7 +4670,7 @@
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4695,7 +4723,7 @@
       <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4748,7 +4776,7 @@
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4798,10 +4826,14 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n"/>
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4854,7 +4886,7 @@
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4907,7 +4939,7 @@
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4957,14 +4989,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="inlineStr">
-        <is>
-          <t>thucnews</t>
-        </is>
-      </c>
+      <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5017,7 +5045,7 @@
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5070,7 +5098,7 @@
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5123,7 +5151,7 @@
       <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5148,27 +5176,27 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5204,7 @@
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5226,10 +5254,14 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n"/>
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5282,7 +5314,7 @@
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5335,50 +5367,315 @@
       <c r="A94" s="1" t="n"/>
       <c r="B94" s="1" t="inlineStr">
         <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n"/>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n"/>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n"/>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n"/>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n"/>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
           <t>TAN</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -5386,21 +5683,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A44:A51"/>
     <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A84:A91"/>
     <mergeCell ref="A4:A11"/>
-    <mergeCell ref="A79:A86"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="A34:A41"/>
     <mergeCell ref="A12:A19"/>
+    <mergeCell ref="A52:A59"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A20:A27"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A50:A54"/>
-    <mergeCell ref="A87:A94"/>
-    <mergeCell ref="A71:A78"/>
-    <mergeCell ref="A63:A70"/>
-    <mergeCell ref="A55:A62"/>
-    <mergeCell ref="A42:A49"/>
+    <mergeCell ref="A68:A75"/>
+    <mergeCell ref="A92:A99"/>
+    <mergeCell ref="A28:A35"/>
+    <mergeCell ref="A60:A67"/>
+    <mergeCell ref="A76:A83"/>
+    <mergeCell ref="A36:A43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/gcd_progress.xlsx
+++ b/results/gcd_progress.xlsx
@@ -474,72 +474,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:L195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>labeled_ratio</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n">
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n">
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>known_cls_ratio</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="D2" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="E2" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="G2" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="H2" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="I2" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="J2" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="L2" s="1" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
+          <t>fold_type</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
           <t>dataset</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
@@ -548,19 +553,19 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t>fold</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
           <t>20NG</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>ALUP</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -597,6 +602,11 @@
         </is>
       </c>
       <c r="K4" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -604,16 +614,12 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>DPN</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -650,6 +656,11 @@
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -657,16 +668,12 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>DeepAligned</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -703,6 +710,11 @@
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -710,16 +722,12 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>GeoID</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -756,6 +764,11 @@
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -763,16 +776,12 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>LOOP</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -809,6 +818,11 @@
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -816,16 +830,12 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>PLM_GCD</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -862,6 +872,11 @@
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -869,16 +884,12 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>SDC</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -915,6 +926,11 @@
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -922,16 +938,12 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>TAN</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -972,23 +984,24 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>DBPedia</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>ALUP</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1025,6 +1038,11 @@
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1032,16 +1050,12 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>DPN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1078,6 +1092,11 @@
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1085,16 +1104,12 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>DeepAligned</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1131,6 +1146,11 @@
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1138,16 +1158,12 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>GeoID</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1184,6 +1200,11 @@
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1191,16 +1212,12 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>LOOP</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1237,6 +1254,11 @@
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1244,16 +1266,12 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>PLM_GCD</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1290,6 +1308,11 @@
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1297,16 +1320,12 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>SDC</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1343,6 +1362,11 @@
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1350,16 +1374,12 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>TAN</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1400,23 +1420,24 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>TREC</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>ALUP</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1453,6 +1474,11 @@
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1460,16 +1486,12 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>DPN</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1506,6 +1528,11 @@
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1513,16 +1540,12 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>DeepAligned</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1559,6 +1582,11 @@
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1566,16 +1594,12 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>GeoID</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1612,6 +1636,11 @@
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1619,16 +1648,12 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B24" s="1" t="n"/>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>LOOP</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1665,6 +1690,11 @@
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1672,16 +1702,12 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B25" s="1" t="n"/>
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>PLM_GCD</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1718,6 +1744,11 @@
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1725,16 +1756,12 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B26" s="1" t="n"/>
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>SDC</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1771,6 +1798,11 @@
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -1778,16 +1810,12 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B27" s="1" t="n"/>
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>TAN</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
@@ -1828,339 +1856,230 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Yahoo</t>
-        </is>
-      </c>
+      <c r="A28" s="1" t="n"/>
       <c r="B28" s="1" t="inlineStr">
         <is>
+          <t>X-Topic</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
           <t>ALUP</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B29" s="1" t="n"/>
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>DPN</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B30" s="1" t="n"/>
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>DeepAligned</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B31" s="1" t="n"/>
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>GeoID</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>LOOP</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B33" s="1" t="n"/>
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>PLM_GCD</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2199,6 +2118,11 @@
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2206,14 +2130,10 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>TAN</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B35" s="1" t="n"/>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2256,21 +2176,18 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>banking</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>ALUP</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="1" t="n"/>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2309,6 +2226,11 @@
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2316,14 +2238,10 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>DPN</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2362,6 +2280,11 @@
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2369,14 +2292,10 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>DeepAligned</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B38" s="1" t="n"/>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2415,6 +2334,11 @@
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2422,14 +2346,10 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>GeoID</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B39" s="1" t="n"/>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2468,6 +2388,11 @@
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2475,14 +2400,10 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>LOOP</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B40" s="1" t="n"/>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2521,6 +2442,11 @@
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2528,14 +2454,10 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>PLM_GCD</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B41" s="1" t="n"/>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2574,6 +2496,11 @@
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2583,12 +2510,12 @@
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>banking</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2627,6 +2554,11 @@
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2634,14 +2566,10 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n"/>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>TAN</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2684,21 +2612,18 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>clinc</t>
-        </is>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>ALUP</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="A44" s="1" t="n"/>
+      <c r="B44" s="1" t="n"/>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2737,6 +2662,11 @@
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2744,14 +2674,10 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n"/>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>DPN</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B45" s="1" t="n"/>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2790,6 +2716,11 @@
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2797,14 +2728,10 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>DeepAligned</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B46" s="1" t="n"/>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2843,6 +2770,11 @@
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2850,14 +2782,10 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n"/>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>GeoID</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B47" s="1" t="n"/>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2896,6 +2824,11 @@
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2903,14 +2836,10 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n"/>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>LOOP</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B48" s="1" t="n"/>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2949,6 +2878,11 @@
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -2956,14 +2890,10 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n"/>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>PLM_GCD</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B49" s="1" t="n"/>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3002,6 +2932,11 @@
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3011,12 +2946,12 @@
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>clinc</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3055,6 +2990,11 @@
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3062,14 +3002,10 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n"/>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>TAN</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B51" s="1" t="n"/>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3112,21 +3048,18 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>ecdt</t>
-        </is>
-      </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>ALUP</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="A52" s="1" t="n"/>
+      <c r="B52" s="1" t="n"/>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3165,6 +3098,11 @@
         </is>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3172,14 +3110,10 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n"/>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>DPN</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B53" s="1" t="n"/>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3218,6 +3152,11 @@
         </is>
       </c>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3225,14 +3164,10 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n"/>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>DeepAligned</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B54" s="1" t="n"/>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3271,6 +3206,11 @@
         </is>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3278,14 +3218,10 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n"/>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>GeoID</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B55" s="1" t="n"/>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3324,6 +3260,11 @@
         </is>
       </c>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3331,14 +3272,10 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n"/>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>LOOP</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B56" s="1" t="n"/>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3377,6 +3314,11 @@
         </is>
       </c>
       <c r="K56" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3384,14 +3326,10 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n"/>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>PLM_GCD</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B57" s="1" t="n"/>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3430,6 +3368,11 @@
         </is>
       </c>
       <c r="K57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3439,12 +3382,12 @@
       <c r="A58" s="1" t="n"/>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>ecdt</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3483,6 +3426,11 @@
         </is>
       </c>
       <c r="K58" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3490,14 +3438,10 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n"/>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>TAN</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B59" s="1" t="n"/>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3540,21 +3484,18 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>hwu</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>ALUP</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="A60" s="1" t="n"/>
+      <c r="B60" s="1" t="n"/>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3593,6 +3534,11 @@
         </is>
       </c>
       <c r="K60" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3600,14 +3546,10 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n"/>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>DPN</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B61" s="1" t="n"/>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3646,6 +3588,11 @@
         </is>
       </c>
       <c r="K61" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3653,14 +3600,10 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n"/>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>DeepAligned</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B62" s="1" t="n"/>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3699,6 +3642,11 @@
         </is>
       </c>
       <c r="K62" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3706,14 +3654,10 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n"/>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>GeoID</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B63" s="1" t="n"/>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3752,6 +3696,11 @@
         </is>
       </c>
       <c r="K63" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3759,14 +3708,10 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n"/>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>LOOP</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B64" s="1" t="n"/>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3805,6 +3750,11 @@
         </is>
       </c>
       <c r="K64" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3812,14 +3762,10 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n"/>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>PLM_GCD</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B65" s="1" t="n"/>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3858,6 +3804,11 @@
         </is>
       </c>
       <c r="K65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -3867,334 +3818,236 @@
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>ele</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n"/>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>TAN</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+      <c r="B67" s="1" t="n"/>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>mcid</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>ALUP</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="A68" s="1" t="n"/>
+      <c r="B68" s="1" t="n"/>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n"/>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>DPN</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B69" s="1" t="n"/>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n"/>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>DeepAligned</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B70" s="1" t="n"/>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n"/>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>GeoID</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B71" s="1" t="n"/>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>hwu</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4233,6 +4086,11 @@
         </is>
       </c>
       <c r="K72" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4240,14 +4098,10 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n"/>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>PLM_GCD</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B73" s="1" t="n"/>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4286,6 +4140,11 @@
         </is>
       </c>
       <c r="K73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4293,14 +4152,10 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n"/>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B74" s="1" t="n"/>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4339,6 +4194,11 @@
         </is>
       </c>
       <c r="K74" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4346,14 +4206,10 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n"/>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>TAN</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B75" s="1" t="n"/>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4396,21 +4252,18 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>ALUP</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="A76" s="1" t="n"/>
+      <c r="B76" s="1" t="n"/>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4449,6 +4302,11 @@
         </is>
       </c>
       <c r="K76" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4456,14 +4314,10 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n"/>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>DPN</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B77" s="1" t="n"/>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4502,6 +4356,11 @@
         </is>
       </c>
       <c r="K77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4509,14 +4368,10 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n"/>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>DeepAligned</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B78" s="1" t="n"/>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4555,6 +4410,11 @@
         </is>
       </c>
       <c r="K78" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4562,14 +4422,10 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n"/>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>GeoID</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B79" s="1" t="n"/>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4608,6 +4464,11 @@
         </is>
       </c>
       <c r="K79" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4617,12 +4478,12 @@
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>mcid</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4661,6 +4522,11 @@
         </is>
       </c>
       <c r="K80" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4668,14 +4534,10 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n"/>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>PLM_GCD</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B81" s="1" t="n"/>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4714,6 +4576,11 @@
         </is>
       </c>
       <c r="K81" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4721,14 +4588,10 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n"/>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B82" s="1" t="n"/>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4767,6 +4630,11 @@
         </is>
       </c>
       <c r="K82" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4774,14 +4642,10 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n"/>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>TAN</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B83" s="1" t="n"/>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4824,21 +4688,18 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="inlineStr">
-        <is>
-          <t>stackoverflow</t>
-        </is>
-      </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>ALUP</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="A84" s="1" t="n"/>
+      <c r="B84" s="1" t="n"/>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4877,6 +4738,11 @@
         </is>
       </c>
       <c r="K84" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4884,14 +4750,10 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n"/>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>DPN</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B85" s="1" t="n"/>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4930,6 +4792,11 @@
         </is>
       </c>
       <c r="K85" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4937,14 +4804,10 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n"/>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>DeepAligned</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B86" s="1" t="n"/>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4983,6 +4846,11 @@
         </is>
       </c>
       <c r="K86" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -4990,14 +4858,10 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n"/>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>GeoID</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B87" s="1" t="n"/>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5036,6 +4900,11 @@
         </is>
       </c>
       <c r="K87" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -5045,12 +4914,12 @@
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5089,6 +4958,11 @@
         </is>
       </c>
       <c r="K88" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -5096,14 +4970,10 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n"/>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>PLM_GCD</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B89" s="1" t="n"/>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5142,6 +5012,11 @@
         </is>
       </c>
       <c r="K89" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -5149,14 +5024,10 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n"/>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B90" s="1" t="n"/>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5195,6 +5066,11 @@
         </is>
       </c>
       <c r="K90" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -5202,14 +5078,10 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n"/>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>TAN</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B91" s="1" t="n"/>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5252,21 +5124,18 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr">
-        <is>
-          <t>thucnews</t>
-        </is>
-      </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>ALUP</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="A92" s="1" t="n"/>
+      <c r="B92" s="1" t="n"/>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5305,6 +5174,11 @@
         </is>
       </c>
       <c r="K92" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -5312,14 +5186,10 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n"/>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>DPN</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B93" s="1" t="n"/>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5358,6 +5228,11 @@
         </is>
       </c>
       <c r="K93" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -5365,14 +5240,10 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n"/>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>DeepAligned</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B94" s="1" t="n"/>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5411,6 +5282,11 @@
         </is>
       </c>
       <c r="K94" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -5418,14 +5294,10 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n"/>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>GeoID</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B95" s="1" t="n"/>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5464,6 +5336,11 @@
         </is>
       </c>
       <c r="K95" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -5473,12 +5350,12 @@
       <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>stackoverflow</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5517,6 +5394,11 @@
         </is>
       </c>
       <c r="K96" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -5524,14 +5406,10 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n"/>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>PLM_GCD</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B97" s="1" t="n"/>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5570,6 +5448,11 @@
         </is>
       </c>
       <c r="K97" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -5577,14 +5460,10 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n"/>
-      <c r="B98" s="1" t="inlineStr">
-        <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
+      <c r="B98" s="1" t="n"/>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5623,6 +5502,11 @@
         </is>
       </c>
       <c r="K98" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t>[0, 1, 2, 3, 4]</t>
         </is>
@@ -5630,74 +5514,2643 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n"/>
-      <c r="B99" s="1" t="inlineStr">
+      <c r="B99" s="1" t="n"/>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n"/>
+      <c r="B100" s="1" t="n"/>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n"/>
+      <c r="B101" s="1" t="n"/>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n"/>
+      <c r="B102" s="1" t="n"/>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n"/>
+      <c r="B103" s="1" t="n"/>
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>TAN</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n"/>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n"/>
+      <c r="B105" s="1" t="n"/>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n"/>
+      <c r="B106" s="1" t="n"/>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n"/>
+      <c r="B107" s="1" t="n"/>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n"/>
+      <c r="B108" s="1" t="n"/>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n"/>
+      <c r="B109" s="1" t="n"/>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n"/>
+      <c r="B110" s="1" t="n"/>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n"/>
+      <c r="B111" s="1" t="n"/>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>TAN</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>imbalance_fold</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>20NG</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n"/>
+      <c r="B113" s="1" t="n"/>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n"/>
+      <c r="B114" s="1" t="n"/>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n"/>
+      <c r="B115" s="1" t="n"/>
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n"/>
+      <c r="B116" s="1" t="n"/>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n"/>
+      <c r="B117" s="1" t="n"/>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n"/>
+      <c r="B118" s="1" t="n"/>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n"/>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>DBPedia</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n"/>
+      <c r="B120" s="1" t="n"/>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n"/>
+      <c r="B121" s="1" t="n"/>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n"/>
+      <c r="B122" s="1" t="n"/>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n"/>
+      <c r="B123" s="1" t="n"/>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n"/>
+      <c r="B124" s="1" t="n"/>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n"/>
+      <c r="B125" s="1" t="n"/>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n"/>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>TREC</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n"/>
+      <c r="B127" s="1" t="n"/>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n"/>
+      <c r="B128" s="1" t="n"/>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n"/>
+      <c r="B129" s="1" t="n"/>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n"/>
+      <c r="B130" s="1" t="n"/>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n"/>
+      <c r="B131" s="1" t="n"/>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n"/>
+      <c r="B132" s="1" t="n"/>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n"/>
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n"/>
+      <c r="B134" s="1" t="n"/>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n"/>
+      <c r="B135" s="1" t="n"/>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n"/>
+      <c r="B136" s="1" t="n"/>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n"/>
+      <c r="B137" s="1" t="n"/>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n"/>
+      <c r="B138" s="1" t="n"/>
+      <c r="C138" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n"/>
+      <c r="B139" s="1" t="n"/>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n"/>
+      <c r="B140" s="1" t="inlineStr">
+        <is>
+          <t>banking</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n"/>
+      <c r="B141" s="1" t="n"/>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n"/>
+      <c r="B142" s="1" t="n"/>
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n"/>
+      <c r="B143" s="1" t="n"/>
+      <c r="C143" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n"/>
+      <c r="B144" s="1" t="n"/>
+      <c r="C144" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n"/>
+      <c r="B145" s="1" t="n"/>
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n"/>
+      <c r="B146" s="1" t="n"/>
+      <c r="C146" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n"/>
+      <c r="B147" s="1" t="inlineStr">
+        <is>
+          <t>clinc</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n"/>
+      <c r="B148" s="1" t="n"/>
+      <c r="C148" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n"/>
+      <c r="B149" s="1" t="n"/>
+      <c r="C149" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n"/>
+      <c r="B150" s="1" t="n"/>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n"/>
+      <c r="B151" s="1" t="n"/>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n"/>
+      <c r="B152" s="1" t="n"/>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n"/>
+      <c r="B153" s="1" t="n"/>
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n"/>
+      <c r="B154" s="1" t="inlineStr">
+        <is>
+          <t>ecdt</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n"/>
+      <c r="B155" s="1" t="n"/>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n"/>
+      <c r="B156" s="1" t="n"/>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n"/>
+      <c r="B157" s="1" t="n"/>
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n"/>
+      <c r="B158" s="1" t="n"/>
+      <c r="C158" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n"/>
+      <c r="B159" s="1" t="n"/>
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n"/>
+      <c r="B160" s="1" t="n"/>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n"/>
+      <c r="B161" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n"/>
+      <c r="B162" s="1" t="n"/>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n"/>
+      <c r="B163" s="1" t="n"/>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n"/>
+      <c r="B164" s="1" t="n"/>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n"/>
+      <c r="B165" s="1" t="n"/>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n"/>
+      <c r="B166" s="1" t="n"/>
+      <c r="C166" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n"/>
+      <c r="B167" s="1" t="n"/>
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n"/>
+      <c r="B168" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n"/>
+      <c r="B169" s="1" t="n"/>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n"/>
+      <c r="B170" s="1" t="n"/>
+      <c r="C170" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n"/>
+      <c r="B171" s="1" t="n"/>
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n"/>
+      <c r="B172" s="1" t="n"/>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n"/>
+      <c r="B173" s="1" t="n"/>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n"/>
+      <c r="B174" s="1" t="n"/>
+      <c r="C174" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n"/>
+      <c r="B175" s="1" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n"/>
+      <c r="B176" s="1" t="n"/>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n"/>
+      <c r="B177" s="1" t="n"/>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n"/>
+      <c r="B178" s="1" t="n"/>
+      <c r="C178" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n"/>
+      <c r="B179" s="1" t="n"/>
+      <c r="C179" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n"/>
+      <c r="B180" s="1" t="n"/>
+      <c r="C180" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n"/>
+      <c r="B181" s="1" t="n"/>
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n"/>
+      <c r="B182" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n"/>
+      <c r="B183" s="1" t="n"/>
+      <c r="C183" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n"/>
+      <c r="B184" s="1" t="n"/>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n"/>
+      <c r="B185" s="1" t="n"/>
+      <c r="C185" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n"/>
+      <c r="B186" s="1" t="n"/>
+      <c r="C186" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n"/>
+      <c r="B187" s="1" t="n"/>
+      <c r="C187" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n"/>
+      <c r="B188" s="1" t="n"/>
+      <c r="C188" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n"/>
+      <c r="B189" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="inlineStr">
+        <is>
+          <t>ALUP</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n"/>
+      <c r="B190" s="1" t="n"/>
+      <c r="C190" s="1" t="inlineStr">
+        <is>
+          <t>DPN</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n"/>
+      <c r="B191" s="1" t="n"/>
+      <c r="C191" s="1" t="inlineStr">
+        <is>
+          <t>DeepAligned</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n"/>
+      <c r="B192" s="1" t="n"/>
+      <c r="C192" s="1" t="inlineStr">
+        <is>
+          <t>GeoID</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n"/>
+      <c r="B193" s="1" t="n"/>
+      <c r="C193" s="1" t="inlineStr">
+        <is>
+          <t>LOOP</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n"/>
+      <c r="B194" s="1" t="n"/>
+      <c r="C194" s="1" t="inlineStr">
+        <is>
+          <t>PLM_GCD</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n"/>
+      <c r="B195" s="1" t="n"/>
+      <c r="C195" s="1" t="inlineStr">
+        <is>
+          <t>SDC</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A44:A51"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A84:A91"/>
-    <mergeCell ref="A4:A11"/>
-    <mergeCell ref="A12:A19"/>
-    <mergeCell ref="A52:A59"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A20:A27"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A68:A75"/>
-    <mergeCell ref="A92:A99"/>
-    <mergeCell ref="A28:A35"/>
-    <mergeCell ref="A60:A67"/>
-    <mergeCell ref="A76:A83"/>
-    <mergeCell ref="A36:A43"/>
+  <mergeCells count="31">
+    <mergeCell ref="B4:B11"/>
+    <mergeCell ref="B66:B71"/>
+    <mergeCell ref="B20:B27"/>
+    <mergeCell ref="B175:B181"/>
+    <mergeCell ref="B147:B153"/>
+    <mergeCell ref="B112:B118"/>
+    <mergeCell ref="B168:B174"/>
+    <mergeCell ref="B50:B57"/>
+    <mergeCell ref="B119:B125"/>
+    <mergeCell ref="B133:B139"/>
+    <mergeCell ref="B189:B195"/>
+    <mergeCell ref="B12:B19"/>
+    <mergeCell ref="B96:B103"/>
+    <mergeCell ref="B72:B79"/>
+    <mergeCell ref="A112:A195"/>
+    <mergeCell ref="B42:B49"/>
+    <mergeCell ref="B58:B65"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="B154:B160"/>
+    <mergeCell ref="A4:A111"/>
+    <mergeCell ref="B126:B132"/>
+    <mergeCell ref="B88:B95"/>
+    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="B140:B146"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="B161:B167"/>
+    <mergeCell ref="B80:B87"/>
+    <mergeCell ref="B182:B188"/>
+    <mergeCell ref="B104:B111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/gcd_progress.xlsx
+++ b/results/gcd_progress.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1866,7 +1866,7 @@
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>X-Topic</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1876,37 +1876,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1918,21 +1930,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1944,37 +1984,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1986,21 +2038,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -2012,37 +2092,49 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -2054,32 +2146,56 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>Yahoo</t>
-        </is>
-      </c>
+      <c r="B34" s="1" t="n"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2133,7 +2249,7 @@
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2184,10 +2300,14 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="1" t="n"/>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>banking</t>
+        </is>
+      </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2241,7 +2361,7 @@
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2295,7 +2415,7 @@
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2349,7 +2469,7 @@
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2403,7 +2523,7 @@
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2457,7 +2577,7 @@
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2508,14 +2628,10 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n"/>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>banking</t>
-        </is>
-      </c>
+      <c r="B42" s="1" t="n"/>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2569,7 +2685,7 @@
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2620,10 +2736,14 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n"/>
-      <c r="B44" s="1" t="n"/>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>clinc</t>
+        </is>
+      </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2677,7 +2797,7 @@
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2731,7 +2851,7 @@
       <c r="B46" s="1" t="n"/>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2785,7 +2905,7 @@
       <c r="B47" s="1" t="n"/>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2839,7 +2959,7 @@
       <c r="B48" s="1" t="n"/>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2893,7 +3013,7 @@
       <c r="B49" s="1" t="n"/>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2944,14 +3064,10 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n"/>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>clinc</t>
-        </is>
-      </c>
+      <c r="B50" s="1" t="n"/>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3005,7 +3121,7 @@
       <c r="B51" s="1" t="n"/>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3056,10 +3172,14 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n"/>
-      <c r="B52" s="1" t="n"/>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>ecdt</t>
+        </is>
+      </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3113,7 +3233,7 @@
       <c r="B53" s="1" t="n"/>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3167,7 +3287,7 @@
       <c r="B54" s="1" t="n"/>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3221,7 +3341,7 @@
       <c r="B55" s="1" t="n"/>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3275,7 +3395,7 @@
       <c r="B56" s="1" t="n"/>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3329,7 +3449,7 @@
       <c r="B57" s="1" t="n"/>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3380,14 +3500,10 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n"/>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>ecdt</t>
-        </is>
-      </c>
+      <c r="B58" s="1" t="n"/>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3441,7 +3557,7 @@
       <c r="B59" s="1" t="n"/>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3492,333 +3608,277 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n"/>
-      <c r="B60" s="1" t="n"/>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>ele</t>
+        </is>
+      </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="n"/>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="n"/>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="n"/>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="n"/>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 3, 4]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="n"/>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0, 3, 4]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>ele</t>
+          <t>hwu</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -3828,33 +3888,49 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n"/>
@@ -3864,23 +3940,51 @@
           <t>DPN</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n"/>
@@ -3892,37 +3996,49 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n"/>
@@ -3934,120 +4050,164 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="n"/>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="n"/>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[0]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>[0, 1, 2, 3, 4]</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n"/>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>hwu</t>
-        </is>
-      </c>
+      <c r="B72" s="1" t="n"/>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4101,7 +4261,7 @@
       <c r="B73" s="1" t="n"/>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4152,10 +4312,14 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n"/>
-      <c r="B74" s="1" t="n"/>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4209,7 +4373,7 @@
       <c r="B75" s="1" t="n"/>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4263,7 +4427,7 @@
       <c r="B76" s="1" t="n"/>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4317,7 +4481,7 @@
       <c r="B77" s="1" t="n"/>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4371,7 +4535,7 @@
       <c r="B78" s="1" t="n"/>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4425,7 +4589,7 @@
       <c r="B79" s="1" t="n"/>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4476,14 +4640,10 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n"/>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>mcid</t>
-        </is>
-      </c>
+      <c r="B80" s="1" t="n"/>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4537,7 +4697,7 @@
       <c r="B81" s="1" t="n"/>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4588,10 +4748,14 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n"/>
-      <c r="B82" s="1" t="n"/>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4645,7 +4809,7 @@
       <c r="B83" s="1" t="n"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4699,7 +4863,7 @@
       <c r="B84" s="1" t="n"/>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4753,7 +4917,7 @@
       <c r="B85" s="1" t="n"/>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4807,7 +4971,7 @@
       <c r="B86" s="1" t="n"/>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4861,7 +5025,7 @@
       <c r="B87" s="1" t="n"/>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4912,14 +5076,10 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n"/>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="B88" s="1" t="n"/>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4973,7 +5133,7 @@
       <c r="B89" s="1" t="n"/>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5024,10 +5184,14 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n"/>
-      <c r="B90" s="1" t="n"/>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5081,7 +5245,7 @@
       <c r="B91" s="1" t="n"/>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5135,7 +5299,7 @@
       <c r="B92" s="1" t="n"/>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5189,7 +5353,7 @@
       <c r="B93" s="1" t="n"/>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5243,7 +5407,7 @@
       <c r="B94" s="1" t="n"/>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5297,7 +5461,7 @@
       <c r="B95" s="1" t="n"/>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5348,14 +5512,10 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n"/>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>stackoverflow</t>
-        </is>
-      </c>
+      <c r="B96" s="1" t="n"/>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5409,7 +5569,7 @@
       <c r="B97" s="1" t="n"/>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5460,10 +5620,14 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n"/>
-      <c r="B98" s="1" t="n"/>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5517,7 +5681,7 @@
       <c r="B99" s="1" t="n"/>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5571,7 +5735,7 @@
       <c r="B100" s="1" t="n"/>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5625,7 +5789,7 @@
       <c r="B101" s="1" t="n"/>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5679,7 +5843,7 @@
       <c r="B102" s="1" t="n"/>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5733,7 +5897,7 @@
       <c r="B103" s="1" t="n"/>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5784,14 +5948,10 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n"/>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>thucnews</t>
-        </is>
-      </c>
+      <c r="B104" s="1" t="n"/>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5845,7 +6005,7 @@
       <c r="B105" s="1" t="n"/>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5895,11 +6055,19 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n"/>
-      <c r="B106" s="1" t="n"/>
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>imbalance_fold</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>20NG</t>
+        </is>
+      </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5907,53 +6075,21 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="n"/>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5961,53 +6097,21 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n"/>
       <c r="B108" s="1" t="n"/>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6015,53 +6119,21 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="n"/>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6069,53 +6141,21 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n"/>
       <c r="B110" s="1" t="n"/>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6123,53 +6163,21 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n"/>
       <c r="B111" s="1" t="n"/>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6177,66 +6185,26 @@
           <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>[0, 1, 2, 3, 4]</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>imbalance_fold</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>20NG</t>
-        </is>
-      </c>
+      <c r="A112" s="1" t="n"/>
+      <c r="B112" s="1" t="n"/>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -6250,15 +6218,19 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n"/>
-      <c r="B113" s="1" t="n"/>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>DBPedia</t>
+        </is>
+      </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -6275,12 +6247,12 @@
       <c r="B114" s="1" t="n"/>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -6297,12 +6269,12 @@
       <c r="B115" s="1" t="n"/>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -6319,12 +6291,12 @@
       <c r="B116" s="1" t="n"/>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -6341,12 +6313,12 @@
       <c r="B117" s="1" t="n"/>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -6363,12 +6335,12 @@
       <c r="B118" s="1" t="n"/>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -6382,19 +6354,15 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n"/>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>DBPedia</t>
-        </is>
-      </c>
+      <c r="B119" s="1" t="n"/>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -6408,15 +6376,19 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n"/>
-      <c r="B120" s="1" t="n"/>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>TREC</t>
+        </is>
+      </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -6433,12 +6405,12 @@
       <c r="B121" s="1" t="n"/>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -6455,12 +6427,12 @@
       <c r="B122" s="1" t="n"/>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -6477,12 +6449,12 @@
       <c r="B123" s="1" t="n"/>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -6499,12 +6471,12 @@
       <c r="B124" s="1" t="n"/>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -6521,12 +6493,12 @@
       <c r="B125" s="1" t="n"/>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -6540,19 +6512,15 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n"/>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>TREC</t>
-        </is>
-      </c>
+      <c r="B126" s="1" t="n"/>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -6566,15 +6534,19 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n"/>
-      <c r="B127" s="1" t="n"/>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -6591,12 +6563,12 @@
       <c r="B128" s="1" t="n"/>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -6613,12 +6585,12 @@
       <c r="B129" s="1" t="n"/>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -6635,12 +6607,12 @@
       <c r="B130" s="1" t="n"/>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -6657,12 +6629,12 @@
       <c r="B131" s="1" t="n"/>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -6679,12 +6651,12 @@
       <c r="B132" s="1" t="n"/>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -6698,19 +6670,15 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n"/>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>Yahoo</t>
-        </is>
-      </c>
+      <c r="B133" s="1" t="n"/>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -6724,15 +6692,19 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n"/>
-      <c r="B134" s="1" t="n"/>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>banking</t>
+        </is>
+      </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -6749,12 +6721,12 @@
       <c r="B135" s="1" t="n"/>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -6771,12 +6743,12 @@
       <c r="B136" s="1" t="n"/>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -6793,12 +6765,12 @@
       <c r="B137" s="1" t="n"/>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -6815,12 +6787,12 @@
       <c r="B138" s="1" t="n"/>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -6837,12 +6809,12 @@
       <c r="B139" s="1" t="n"/>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -6856,19 +6828,15 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n"/>
-      <c r="B140" s="1" t="inlineStr">
-        <is>
-          <t>banking</t>
-        </is>
-      </c>
+      <c r="B140" s="1" t="n"/>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -6882,15 +6850,19 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n"/>
-      <c r="B141" s="1" t="n"/>
+      <c r="B141" s="1" t="inlineStr">
+        <is>
+          <t>clinc</t>
+        </is>
+      </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -6907,12 +6879,12 @@
       <c r="B142" s="1" t="n"/>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -6929,12 +6901,12 @@
       <c r="B143" s="1" t="n"/>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -6951,12 +6923,12 @@
       <c r="B144" s="1" t="n"/>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -6973,12 +6945,12 @@
       <c r="B145" s="1" t="n"/>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -6995,12 +6967,12 @@
       <c r="B146" s="1" t="n"/>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -7014,19 +6986,15 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n"/>
-      <c r="B147" s="1" t="inlineStr">
-        <is>
-          <t>clinc</t>
-        </is>
-      </c>
+      <c r="B147" s="1" t="n"/>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -7040,15 +7008,19 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n"/>
-      <c r="B148" s="1" t="n"/>
+      <c r="B148" s="1" t="inlineStr">
+        <is>
+          <t>ecdt</t>
+        </is>
+      </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -7065,12 +7037,12 @@
       <c r="B149" s="1" t="n"/>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -7087,12 +7059,12 @@
       <c r="B150" s="1" t="n"/>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -7109,12 +7081,12 @@
       <c r="B151" s="1" t="n"/>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -7131,12 +7103,12 @@
       <c r="B152" s="1" t="n"/>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -7153,12 +7125,12 @@
       <c r="B153" s="1" t="n"/>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7172,19 +7144,15 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n"/>
-      <c r="B154" s="1" t="inlineStr">
-        <is>
-          <t>ecdt</t>
-        </is>
-      </c>
+      <c r="B154" s="1" t="n"/>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7198,15 +7166,19 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n"/>
-      <c r="B155" s="1" t="n"/>
+      <c r="B155" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7223,12 +7195,12 @@
       <c r="B156" s="1" t="n"/>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7245,12 +7217,12 @@
       <c r="B157" s="1" t="n"/>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7267,12 +7239,12 @@
       <c r="B158" s="1" t="n"/>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7289,12 +7261,12 @@
       <c r="B159" s="1" t="n"/>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7311,12 +7283,12 @@
       <c r="B160" s="1" t="n"/>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7330,19 +7302,15 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n"/>
-      <c r="B161" s="1" t="inlineStr">
-        <is>
-          <t>hwu</t>
-        </is>
-      </c>
+      <c r="B161" s="1" t="n"/>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7356,15 +7324,19 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n"/>
-      <c r="B162" s="1" t="n"/>
+      <c r="B162" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7381,12 +7353,12 @@
       <c r="B163" s="1" t="n"/>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7403,12 +7375,12 @@
       <c r="B164" s="1" t="n"/>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7425,12 +7397,12 @@
       <c r="B165" s="1" t="n"/>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7447,12 +7419,12 @@
       <c r="B166" s="1" t="n"/>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7469,12 +7441,12 @@
       <c r="B167" s="1" t="n"/>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7488,19 +7460,15 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n"/>
-      <c r="B168" s="1" t="inlineStr">
-        <is>
-          <t>mcid</t>
-        </is>
-      </c>
+      <c r="B168" s="1" t="n"/>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -7514,15 +7482,19 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n"/>
-      <c r="B169" s="1" t="n"/>
+      <c r="B169" s="1" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -7539,12 +7511,12 @@
       <c r="B170" s="1" t="n"/>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -7561,12 +7533,12 @@
       <c r="B171" s="1" t="n"/>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -7583,12 +7555,12 @@
       <c r="B172" s="1" t="n"/>
       <c r="C172" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -7605,12 +7577,12 @@
       <c r="B173" s="1" t="n"/>
       <c r="C173" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -7627,12 +7599,12 @@
       <c r="B174" s="1" t="n"/>
       <c r="C174" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -7646,19 +7618,15 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n"/>
-      <c r="B175" s="1" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
+      <c r="B175" s="1" t="n"/>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -7672,15 +7640,19 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n"/>
-      <c r="B176" s="1" t="n"/>
+      <c r="B176" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
       <c r="C176" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -7697,12 +7669,12 @@
       <c r="B177" s="1" t="n"/>
       <c r="C177" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -7719,12 +7691,12 @@
       <c r="B178" s="1" t="n"/>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -7741,12 +7713,12 @@
       <c r="B179" s="1" t="n"/>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -7763,12 +7735,12 @@
       <c r="B180" s="1" t="n"/>
       <c r="C180" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -7785,12 +7757,12 @@
       <c r="B181" s="1" t="n"/>
       <c r="C181" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -7804,19 +7776,15 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n"/>
-      <c r="B182" s="1" t="inlineStr">
-        <is>
-          <t>stackoverflow</t>
-        </is>
-      </c>
+      <c r="B182" s="1" t="n"/>
       <c r="C182" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -7830,15 +7798,19 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n"/>
-      <c r="B183" s="1" t="n"/>
+      <c r="B183" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>DPN</t>
+          <t>ALUP</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -7855,12 +7827,12 @@
       <c r="B184" s="1" t="n"/>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t>DeepAligned</t>
+          <t>DPN</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -7877,12 +7849,12 @@
       <c r="B185" s="1" t="n"/>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t>GeoID</t>
+          <t>DeepAligned</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -7899,12 +7871,12 @@
       <c r="B186" s="1" t="n"/>
       <c r="C186" s="1" t="inlineStr">
         <is>
-          <t>LOOP</t>
+          <t>GeoID</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -7921,12 +7893,12 @@
       <c r="B187" s="1" t="n"/>
       <c r="C187" s="1" t="inlineStr">
         <is>
-          <t>PLM_GCD</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -7943,12 +7915,12 @@
       <c r="B188" s="1" t="n"/>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>SDC</t>
+          <t>PLM_GCD</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>[0, 1, 2]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -7962,19 +7934,15 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n"/>
-      <c r="B189" s="1" t="inlineStr">
-        <is>
-          <t>thucnews</t>
-        </is>
-      </c>
+      <c r="B189" s="1" t="n"/>
       <c r="C189" s="1" t="inlineStr">
         <is>
-          <t>ALUP</t>
+          <t>SDC</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>[0, 1]</t>
+          <t>[0, 1, 2, 3, 4]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -7986,171 +7954,38 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
     </row>
-    <row r="190">
-      <c r="A190" s="1" t="n"/>
-      <c r="B190" s="1" t="n"/>
-      <c r="C190" s="1" t="inlineStr">
-        <is>
-          <t>DPN</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>[0, 1]</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="1" t="n"/>
-      <c r="B191" s="1" t="n"/>
-      <c r="C191" s="1" t="inlineStr">
-        <is>
-          <t>DeepAligned</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>[0, 1]</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="1" t="n"/>
-      <c r="B192" s="1" t="n"/>
-      <c r="C192" s="1" t="inlineStr">
-        <is>
-          <t>GeoID</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>[0, 1]</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="1" t="n"/>
-      <c r="B193" s="1" t="n"/>
-      <c r="C193" s="1" t="inlineStr">
-        <is>
-          <t>LOOP</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>[0, 1]</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="1" t="n"/>
-      <c r="B194" s="1" t="n"/>
-      <c r="C194" s="1" t="inlineStr">
-        <is>
-          <t>PLM_GCD</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>[0, 1]</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="1" t="n"/>
-      <c r="B195" s="1" t="n"/>
-      <c r="C195" s="1" t="inlineStr">
-        <is>
-          <t>SDC</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>[0, 1]</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="30">
     <mergeCell ref="B4:B11"/>
-    <mergeCell ref="B66:B71"/>
     <mergeCell ref="B20:B27"/>
-    <mergeCell ref="B175:B181"/>
-    <mergeCell ref="B147:B153"/>
-    <mergeCell ref="B112:B118"/>
-    <mergeCell ref="B168:B174"/>
-    <mergeCell ref="B50:B57"/>
-    <mergeCell ref="B119:B125"/>
-    <mergeCell ref="B133:B139"/>
-    <mergeCell ref="B189:B195"/>
+    <mergeCell ref="A4:A105"/>
+    <mergeCell ref="B90:B97"/>
+    <mergeCell ref="B66:B73"/>
+    <mergeCell ref="B162:B168"/>
+    <mergeCell ref="A106:A189"/>
+    <mergeCell ref="B127:B133"/>
     <mergeCell ref="B12:B19"/>
-    <mergeCell ref="B96:B103"/>
-    <mergeCell ref="B72:B79"/>
-    <mergeCell ref="A112:A195"/>
-    <mergeCell ref="B42:B49"/>
-    <mergeCell ref="B58:B65"/>
+    <mergeCell ref="B183:B189"/>
+    <mergeCell ref="B52:B59"/>
     <mergeCell ref="G1:I1"/>
-    <mergeCell ref="B154:B160"/>
-    <mergeCell ref="A4:A111"/>
-    <mergeCell ref="B126:B132"/>
-    <mergeCell ref="B88:B95"/>
-    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="B98:B105"/>
+    <mergeCell ref="B141:B147"/>
+    <mergeCell ref="B113:B119"/>
+    <mergeCell ref="B60:B65"/>
+    <mergeCell ref="B169:B175"/>
+    <mergeCell ref="B44:B51"/>
+    <mergeCell ref="B82:B89"/>
+    <mergeCell ref="B134:B140"/>
+    <mergeCell ref="B28:B35"/>
     <mergeCell ref="D1:F1"/>
-    <mergeCell ref="B140:B146"/>
+    <mergeCell ref="B106:B112"/>
     <mergeCell ref="J1:L1"/>
-    <mergeCell ref="B34:B41"/>
-    <mergeCell ref="B161:B167"/>
-    <mergeCell ref="B80:B87"/>
-    <mergeCell ref="B182:B188"/>
-    <mergeCell ref="B104:B111"/>
+    <mergeCell ref="B74:B81"/>
+    <mergeCell ref="B148:B154"/>
+    <mergeCell ref="B155:B161"/>
+    <mergeCell ref="B120:B126"/>
+    <mergeCell ref="B36:B43"/>
+    <mergeCell ref="B176:B182"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
